--- a/medical_surveys_questionnaires/048_mental_health_stigma_in_healthcare_settings_survey--medical_surveys_questionnaires.xlsx
+++ b/medical_surveys_questionnaires/048_mental_health_stigma_in_healthcare_settings_survey--medical_surveys_questionnaires.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'strongly_agree',_'value':_'strongly_agree'}</t>
+          <t>strongly_agree</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'strongly_agree', 'value': 'strongly_agree'}</t>
+          <t>strongly agree</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_agree',_'value':_'somewhat_agree'}</t>
+          <t>somewhat_agree</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'somewhat_agree', 'value': 'somewhat_agree'}</t>
+          <t>somewhat agree</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'neutral',_'value':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'neutral', 'value': 'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_disagree',_'value':_'somewhat_disagree'}</t>
+          <t>somewhat_disagree</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'somewhat_disagree', 'value': 'somewhat_disagree'}</t>
+          <t>somewhat disagree</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'strongly_disagree',_'value':_'strongly_disagree'}</t>
+          <t>strongly_disagree</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'strongly_disagree', 'value': 'strongly_disagree'}</t>
+          <t>strongly disagree</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'very_high'}</t>
+          <t>very_high</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'very_high'}</t>
+          <t>very high</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'high'}</t>
+          <t>high</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'low'}</t>
+          <t>low</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'very_low'}</t>
+          <t>very_low</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'very_low'}</t>
+          <t>very low</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'hospital',_'value':_'hospital'}</t>
+          <t>hospital</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Hospital', 'value': 'Hospital'}</t>
+          <t>Hospital</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'clinic',_'value':_'clinic'}</t>
+          <t>clinic</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Clinic', 'value': 'Clinic'}</t>
+          <t>Clinic</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Other', 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'high_school_diploma_or_equivalent',_'value':_'high_school_diploma_or_equivalent'}</t>
+          <t>high_school_diploma_or_equivalent</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'High School Diploma or Equivalent', 'value': 'High School Diploma or Equivalent'}</t>
+          <t>High School Diploma or Equivalent</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'bachelors',_'value':_'bachelors'}</t>
+          <t>bachelors</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Bachelors', 'value': 'Bachelors'}</t>
+          <t>Bachelors</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'master',_'value':_'master'}</t>
+          <t>master</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Master', 'value': 'Master'}</t>
+          <t>Master</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'doctoral',_'value':_'doctoral'}</t>
+          <t>doctoral</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Doctoral', 'value': 'Doctoral'}</t>
+          <t>Doctoral</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Other', 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'morning',_'value':_'morning'}</t>
+          <t>morning</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Morning', 'value': 'Morning'}</t>
+          <t>Morning</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'afternoon',_'value':_'afternoon'}</t>
+          <t>afternoon</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Afternoon', 'value': 'Afternoon'}</t>
+          <t>Afternoon</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'evening',_'value':_'evening'}</t>
+          <t>evening</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Evening', 'value': 'Evening'}</t>
+          <t>Evening</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'night',_'value':_'night'}</t>
+          <t>night</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Night', 'value': 'Night'}</t>
+          <t>Night</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'clinical',_'value':_'clinical'}</t>
+          <t>clinical</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Clinical', 'value': 'Clinical'}</t>
+          <t>Clinical</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'non-clinical',_'value':_'non-clinical'}</t>
+          <t>non-clinical</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Non-Clinical', 'value': 'Non-Clinical'}</t>
+          <t>Non-Clinical</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'full-time',_'value':_'full-time'}</t>
+          <t>full-time</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Full-time', 'value': 'Full-time'}</t>
+          <t>Full-time</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'part-time',_'value':_'part-time'}</t>
+          <t>part-time</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Part-time', 'value': 'Part-time'}</t>
+          <t>Part-time</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'contract',_'value':_'contract'}</t>
+          <t>contract</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'Contract', 'value': 'Contract'}</t>
+          <t>Contract</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'temporary',_'value':_'temporary'}</t>
+          <t>temporary</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'Temporary', 'value': 'Temporary'}</t>
+          <t>Temporary</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
